--- a/강의예제/5장_데이터_정리부터_데이터_필터링까지/5장_종합문제.xlsx
+++ b/강의예제/5장_데이터_정리부터_데이터_필터링까지/5장_종합문제.xlsx
@@ -1321,9 +1321,10 @@
           <t>5-08</t>
         </is>
       </c>
-      <c r="E8" s="15">
-        <f>SUBTOTAL(9,F6:F16). 9 는 합계입니다.</f>
-        <v/>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>=SUBTOTAL(9,F6:F16). 9 는 합계입니다.</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
